--- a/artfynd/A 6986-2024 artfynd.xlsx
+++ b/artfynd/A 6986-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135596567</v>
       </c>
       <c r="B2" t="n">
-        <v>99115</v>
+        <v>99162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,6 +783,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Hannu Hietamäki</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Hannu Hietamäki</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>

--- a/artfynd/A 6986-2024 artfynd.xlsx
+++ b/artfynd/A 6986-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135596567</v>
       </c>
       <c r="B2" t="n">
-        <v>99162</v>
+        <v>99189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6986-2024 artfynd.xlsx
+++ b/artfynd/A 6986-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135596567</v>
       </c>
       <c r="B2" t="n">
-        <v>99194</v>
+        <v>99196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6986-2024 artfynd.xlsx
+++ b/artfynd/A 6986-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135596567</v>
       </c>
       <c r="B2" t="n">
-        <v>99196</v>
+        <v>99213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6986-2024 artfynd.xlsx
+++ b/artfynd/A 6986-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135596567</v>
       </c>
       <c r="B2" t="n">
-        <v>99213</v>
+        <v>99214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6986-2024 artfynd.xlsx
+++ b/artfynd/A 6986-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135596567</v>
       </c>
       <c r="B2" t="n">
-        <v>99214</v>
+        <v>99215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
